--- a/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
@@ -1075,7 +1075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G155"/>
+  <dimension ref="C1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1184,7 +1184,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="155" ht="13.5"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>#</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>1000021;1</t>
+  </si>
+  <si>
+    <t>戒指洗练相关</t>
+  </si>
+  <si>
+    <t>500;5;20;0#0#0|2000;5;20;0#0#0|5000;-1;0;1012#1#25</t>
+  </si>
+  <si>
+    <t>消耗元宝;成功率;保底次数;附加属性</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1084,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G10"/>
+  <dimension ref="C1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1083,7 +1092,7 @@
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="89.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.875" style="2" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -1184,6 +1193,20 @@
         <v>12</v>
       </c>
     </row>
+    <row r="11" spans="3:7">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
+++ b/Unity/Assets/Config/Excel/GlobalValueConfig.xlsx
@@ -71,7 +71,7 @@
     <t>戒指洗练相关</t>
   </si>
   <si>
-    <t>500;5;20;0#0#0|2000;5;20;0#0#0|5000;-1;0;1012#1#25</t>
+    <t>500;5;20;0#0#0|2000;5;20;0#0#0|5000;1;9999;1012#1#25</t>
   </si>
   <si>
     <t>消耗元宝;成功率;保底次数;附加属性</t>
